--- a/Metadata_shinny.xlsx
+++ b/Metadata_shinny.xlsx
@@ -470,7 +470,8 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -534,7 +535,8 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -598,7 +600,8 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -662,7 +665,8 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -726,7 +730,8 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -790,7 +795,8 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -972,7 +978,8 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1036,7 +1043,8 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1100,7 +1108,8 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1164,7 +1173,8 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1228,7 +1238,8 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1292,7 +1303,8 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1356,7 +1368,8 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1420,7 +1433,8 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1484,7 +1498,8 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2256,7 +2271,8 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2320,7 +2336,8 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2384,7 +2401,8 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2448,7 +2466,8 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2866,7 +2885,8 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio. Debido a los cambios en la forma de relevamiento en el módulo de educación en las ECH 2020 y 2021, este indicador se presenta hasta 2019 y se continúa en 2022, no siendo comparable con la serie anterior.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2930,7 +2950,8 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio. Debido a los cambios en la forma de relevamiento en el módulo de educación en las ECH 2020 y 2021, este indicador se presenta hasta 2019 y se continúa en 2022, no siendo comparable con la serie anterior.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3171,7 +3192,8 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. A partir de 2020 cambia el modo de relevar cobertura de salud. Antes de esta fecha se les consultaba a los/as encuestados por cobertura en cada uno de los prestadores posibles. Durante el 2020 y el primer semestre de 2021, se relevó únicamente el principal prestador de salud. En el segundo semestre de 2021 se relevó el prestador principal y secundario, hecho que habilita reconstruir un indicador más próximo al calculado antes de 2019. Para 2021, este indicador se calcula únicamente a partir de la implantación de modalidad panel del segundo semestre de 2021. Dados los cambios metodológicos en la formulación de las preguntas, no se incorpora a la serie el año 2020 y tampoco se considera la información del primer semestre de 2021. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3235,7 +3257,8 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. A partir de 2020 cambia el modo de relevar cobertura de salud. Antes de esta fecha se les consultaba a los/as encuestados por cobertura en cada uno de los prestadores posibles. Durante el 2020 y el primer semestre de 2021, se relevó únicamente el principal prestador de salud. En el segundo semestre de 2021 se relevó el prestador principal y secundario, hecho que habilita reconstruir un indicador más próximo al calculado antes de 2019. Para 2021, este indicador se calcula únicamente a partir de la implantación de modalidad panel del segundo semestre de 2021. Dados los cambios metodológicos en la formulación de las preguntas, no se incorpora a la serie el año 2020 y tampoco se considera la información del primer semestre de 2021. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3299,7 +3322,8 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. A partir de 2020 cambia el modo de relevar cobertura de salud. Antes de esta fecha se les consultaba a los/as encuestados por cobertura en cada uno de los prestadores posibles. Durante el 2020 y el primer semestre de 2021, se relevó únicamente el principal prestador de salud. En el segundo semestre de 2021 se relevó el prestador principal y secundario, hecho que habilita reconstruir un indicador más próximo al calculado antes de 2019. Para 2021, este indicador se calcula únicamente a partir de la implantación de modalidad panel del segundo semestre de 2021. Dados los cambios metodológicos en la formulación de las preguntas, no se incorpora a la serie el año 2020 y tampoco se considera la información del primer semestre de 2021. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3363,7 +3387,8 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. A partir de 2020 cambia el modo de relevar cobertura de salud. Antes de esta fecha se les consultaba a los/as encuestados por cobertura en cada uno de los prestadores posibles. Durante el 2020 y el primer semestre de 2021, se relevó únicamente el principal prestador de salud. En el segundo semestre de 2021 se relevó el prestador principal y secundario, hecho que habilita reconstruir un indicador más próximo al calculado antes de 2019. Para 2021, este indicador se calcula únicamente a partir de la implantación de modalidad panel del segundo semestre de 2021. Dados los cambios metodológicos en la formulación de las preguntas, no se incorpora a la serie el año 2020 y tampoco se considera la información del primer semestre de 2021. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.</t>
+          <t>Desde marzo de 2020 hasta junio de 2021 se interrumpió el relevamiento presencial y se aplicó de manera telefónica un cuestionario restringido con el objetivo de continuar publicando los indicadores de ingresos y mercado de trabajo. En ese período la encuesta pasó a ser de paneles rotativos elegidos al azar a partir de los casos respondentes del año anterior. En julio de 2021 el INE retomó la realización de encuestas presenciales, pero introdujo un cambio metodológico, ya que la ECH pasa a ser una encuesta de panel rotativo con periodicidad mensual compuesta por seis paneles o grupos de rotación, cada uno de los cuales es una muestra representativa de la población. Con esta nueva metodología, cada hogar seleccionado participa durante seis meses de la ECH. Considerando que en la base 2021 hay hogares que presentan más de un jefe y otros en los que no hay ninguno, el indicador para 2021 se presenta para todos los hogares que presentan uno y solo un jefe. A partir de 2022 el indicador se calcula a partir de la base de implantación anual. La transparencia de colores representa cambios metodológicos en el relevamiento de las ECH. La línea se discontinúa en aquellos años en que ocurre el cambio.
+Desde 2025, en la ECH no se incluye la variable HT11 para los ingresos totales del hogar. En su lugar se usa la variable de ingreso disponible ajustado (YDA) para el cálculo de los indicadores de ingresos y pobreza, así como para la construcción de los quintiles de ingresos.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
